--- a/LOV3_HTX_Q2_2026_PL.xlsx
+++ b/LOV3_HTX_Q2_2026_PL.xlsx
@@ -1642,13 +1642,13 @@
         <v>23989.32</v>
       </c>
       <c r="D64" s="9" t="n">
-        <v>11377.89</v>
+        <v>5877.89</v>
       </c>
       <c r="E64" s="9" t="n">
-        <v>46415.23</v>
+        <v>40915.23</v>
       </c>
       <c r="F64" s="10" t="n">
-        <v>0.02423948971351185</v>
+        <v>0.02136721711194734</v>
       </c>
     </row>
     <row r="65">
@@ -1796,13 +1796,13 @@
         <v>70250.84</v>
       </c>
       <c r="D71" s="12" t="n">
-        <v>91621.53</v>
+        <v>86121.53</v>
       </c>
       <c r="E71" s="12" t="n">
-        <v>179117.73</v>
+        <v>173617.73</v>
       </c>
       <c r="F71" s="13" t="n">
-        <v>0.09354089969698726</v>
+        <v>0.09066862709542274</v>
       </c>
     </row>
     <row r="73">
@@ -1852,13 +1852,13 @@
         <v>0</v>
       </c>
       <c r="D75" s="9" t="n">
-        <v>0</v>
+        <v>5500</v>
       </c>
       <c r="E75" s="9" t="n">
-        <v>2489.75</v>
+        <v>7989.75</v>
       </c>
       <c r="F75" s="10" t="n">
-        <v>0.001300225583590045</v>
+        <v>0.004172498185154557</v>
       </c>
     </row>
     <row r="76">
@@ -1896,13 +1896,13 @@
         <v>2342.9</v>
       </c>
       <c r="D77" s="12" t="n">
-        <v>3450</v>
+        <v>8950</v>
       </c>
       <c r="E77" s="12" t="n">
-        <v>9057.65</v>
+        <v>14557.65</v>
       </c>
       <c r="F77" s="13" t="n">
-        <v>0.004730189078101965</v>
+        <v>0.007602461679666477</v>
       </c>
     </row>
     <row r="79">
